--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
@@ -1,19 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{0F06DEA4-4FD7-48BB-9EFF-FE9D6BC94304}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{32E3B551-0A7E-43F7-B174-171592750CC1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
+    <workbookView activeTab="18" firstSheet="17" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet name="CCDeferredCC" r:id="rId1" sheetId="1"/>
+    <sheet name="PayNowCCNoCF" r:id="rId2" sheetId="2"/>
+    <sheet name="NoModifyAmountCC" r:id="rId3" sheetId="5"/>
+    <sheet name="NoModifyBillingAddressCC" r:id="rId4" sheetId="6"/>
+    <sheet name="VerifyPaymentConfPayNowCC" r:id="rId5" sheetId="7"/>
+    <sheet name="PayNowCCSCF" r:id="rId6" sheetId="3"/>
+    <sheet name="SCFCCVerbiage" r:id="rId7" sheetId="8"/>
+    <sheet name="PayNowCCDCF" r:id="rId8" sheetId="4"/>
+    <sheet name="DCFCCVerbiage" r:id="rId9" sheetId="9"/>
+    <sheet name="CMCAutopayCC" r:id="rId10" sheetId="10"/>
+    <sheet name="CMCDeferredCC" r:id="rId11" sheetId="11"/>
+    <sheet name="ModifyStaticTextAutopayCC" r:id="rId12" sheetId="12"/>
+    <sheet name="ModifySuccessAutopayCC" r:id="rId13" sheetId="13"/>
+    <sheet name="CancelStaticTextAutopayCC" r:id="rId14" sheetId="14"/>
+    <sheet name="CancelSuccessAutopayCC" r:id="rId15" sheetId="15"/>
+    <sheet name="CancelStaticTextDeferredCC" r:id="rId16" sheetId="16"/>
+    <sheet name="CancelSuccessDeferredCC" r:id="rId17" sheetId="17"/>
+    <sheet name="ModifyStaticTextDeferredCC" r:id="rId18" sheetId="18"/>
+    <sheet name="ModifySuccessDeferredCC" r:id="rId19" sheetId="19"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="176">
   <si>
     <t>Result</t>
   </si>
@@ -72,9 +90,6 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu Feb 12 20:25:29 IST 2026</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -108,10 +123,454 @@
     <t>3.0</t>
   </si>
   <si>
+    <t>Wed Mar 04 19:53:53 IST 2026</t>
+  </si>
+  <si>
+    <t>972</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:51:39 IST 2026</t>
+  </si>
+  <si>
+    <t>985</t>
+  </si>
+  <si>
+    <t>986</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Wed Mar 04 19:53:53 IST 2026</t>
+    <t>Wed Apr 15 20:06:59 IST 2026</t>
+  </si>
+  <si>
+    <t>988</t>
+  </si>
+  <si>
+    <t>Thu Apr 16 21:14:09 IST 2026</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Tue Mar 24 20:02:18 IST 2026</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 19:31:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 19:51:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:32:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:45:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:18:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:25:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:30:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:34:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:41:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:55:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:58:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:59:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:37:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:38:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:58:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 22:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:00:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:18:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:21:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:28:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:29:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:30:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:32:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:42:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:45:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:47:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:53:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:58:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:59:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:00:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:09:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:13:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:20:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:20:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 00:25:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 19:07:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 19:27:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 19:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 19:50:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 20:33:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 20:58:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 21:23:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 21:37:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 28 23:43:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:13:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:26:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:27:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:28:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:30:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:48:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 17:50:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 18:05:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 18:08:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 18:10:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 18:12:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 18:28:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 19:25:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 19:28:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 19:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 19:48:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 20:06:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 20:09:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 20:49:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 21:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 29 21:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:06:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:13:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:18:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:23:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:27:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:32:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:40:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:43:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:44:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:52:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:55:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 19:57:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:09:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:26:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:27:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:30:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:45:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:47:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:50:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:54:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:59:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 21:57:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 21:44:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:04:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:09:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:15:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:20:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:25:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:29:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:33:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:47:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:48:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 22:49:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:03:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:04:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:06:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:07:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:20:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:21:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:22:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:24:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:40:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:42:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:46:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:49:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:54:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 00:54:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 00:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 20:33:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 20:36:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 20:45:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -163,12 +622,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" quotePrefix="1" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle builtinId="0" name="Normal" xfId="0"/>
@@ -504,41 +967,1748 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B62B5D-80BF-48B2-B759-17E0231A17F8}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2595893-F564-402F-B741-D06FC8F9A57A}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.5546875" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE7D31B-3B51-4B73-8756-2083F5943642}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FC4665-EB03-485D-A4A8-6B4E63BA428C}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10BE5FF-98C1-4C25-AD38-BAE7F568AF90}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{829D57EA-7BB6-4632-8A7B-652C7090A7B2}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42B662D5-46CE-432A-89CD-373289D37E11}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F656F751-B34C-4950-9D70-04CF0988D969}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B44FB76-7C27-401A-A168-C8FDC663384E}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90B1FB22-2FF2-4EED-BB24-9F44F57FDA31}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="N2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FEFD7B-3EF4-4F7A-9D19-E2DD13F70A7A}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01D904C4-30CE-422E-8FD6-427FC9AA8A3F}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CBCDE5C-3478-401D-BF03-201E275E4EED}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AE8036-DC24-484E-8C3C-0B3490CCD29C}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2958D932-E864-4E65-B35D-6C2CFFA69331}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{704C9A3D-D5B6-43AA-9E5F-D028346C5842}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703B31DE-2B66-4AC7-82E0-612DA620517B}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017C3DA6-C030-4DC9-9E5C-1ECC7AC0941C}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
+++ b/KatalonData/IWPBootstrapData/VRelayPaymentsCC_30.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="218">
   <si>
     <t>Result</t>
   </si>
@@ -571,6 +571,132 @@
   </si>
   <si>
     <t>Wed May 06 20:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 11:12:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 11:14:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:56:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:57:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 22:58:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:00:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:16:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:21:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:30:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:35:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:39:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:40:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:42:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:43:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 23:59:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:01:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:03:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:04:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:14:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:32:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:33:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:35:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:51:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:54:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:58:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:59:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:00:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:01:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:09:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:20:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 19:19:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 19:46:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 19:51:58 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1189,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1160,7 +1286,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1256,7 +1382,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1350,7 +1476,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1444,7 +1570,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>215</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1535,10 +1661,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1632,7 +1758,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1728,7 +1854,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1824,7 +1950,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -1920,7 +2046,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2016,7 +2142,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2110,7 +2236,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2206,7 +2332,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2302,7 +2428,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2394,7 +2520,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2488,7 +2614,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2582,7 +2708,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
@@ -2676,7 +2802,7 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="1" t="s">
